--- a/draftTAPPs/EBSD_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/EBSD_TAPP_draft_v2.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Timms, Nicholas E</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>2023-11-16</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>2023-11-16</t>
         </is>
       </c>
     </row>

--- a/draftTAPPs/EBSD_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/EBSD_TAPP_draft_v2.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Timms, Nicholas E</t>
+          <t>Claude assisted</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7. EBSD Acquisition and Indexing</t>
+          <t>Procedure Author Description</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>How this draft was produced.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2362,43 +2382,18 @@
       <c r="I49" t="inlineStr">
         <is>
           <t>(none)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Draft generated by Claude (Anthropic) under human review, from analysis of ADA metadata records and the 14 Curtin University method-description documents attached to them. Parameter values and tier assignments are derived, not authored by the laboratory.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Accelerating Voltage</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Electron beam accelerating voltage.</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Editable</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Number + unit</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>20 kV (observed 5, 10, 15, 20)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>7. EBSD Acquisition and Indexing</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2409,23 +2404,18 @@
       <c r="I50" t="inlineStr">
         <is>
           <t>(none)</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>20 kV</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Beam Current</t>
+          <t>Accelerating Voltage</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Beam current at the sample.</t>
+          <t>Electron beam accelerating voltage.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2445,7 +2435,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>~1.5 nA (observed ~1.0 to ~1.5)</t>
+          <t>20 kV (observed 5, 10, 15, 20)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2465,19 +2455,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>~1.5 nA</t>
+          <t>20 kV</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Stage Tilt</t>
+          <t>Beam Current</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Specimen tilt toward the EBSD detector.</t>
+          <t>Beam current at the sample.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2487,7 +2477,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Read-Only</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2497,12 +2487,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70 deg</t>
+          <t>~1.5 nA (observed ~1.0 to ~1.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Constant in all 14 documents. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2517,29 +2507,29 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>70 deg</t>
+          <t>~1.5 nA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Working Distance</t>
+          <t>Stage Tilt</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Working distance during mapping.</t>
+          <t>Specimen tilt toward the EBSD detector.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2549,12 +2539,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17.8-18.3 mm (observed 15 to 18.3)</t>
+          <t>70 deg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Constant in all 14 documents. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2569,19 +2559,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>17.8-18.3 mm</t>
+          <t>70 deg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EBSD Camera Exposure Time</t>
+          <t>Working Distance</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Exposure time per EBSD pattern.</t>
+          <t>Working distance during mapping.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2601,7 +2591,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20-25 ms (observed 15 to 25)</t>
+          <t>17.8-18.3 mm (observed 15 to 18.3)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2621,44 +2611,44 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>20-25 ms</t>
+          <t>17.8-18.3 mm</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EBSD Camera Speed Setting</t>
+          <t>EBSD Camera Exposure Time</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Named camera speed mode of the EBSD detector. Recorded separately from the pattern resolution it implies: the two are distinct settings even though the source states them together as "Speed 1 (622 x 512 pixels)".</t>
+          <t>Exposure time per EBSD pattern.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Read-Only</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Controlled list</t>
+          <t>Number + unit</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Speed 1</t>
+          <t>20-25 ms (observed 15 to 25)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Constant in the 12 documents that state it. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2673,19 +2663,19 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Speed 1</t>
+          <t>20-25 ms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EBSD Pattern Resolution</t>
+          <t>EBSD Camera Speed Setting</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pattern resolution in detector pixels, the second half of the source's "Speed 1 (622 x 512 pixels)".</t>
+          <t>Named camera speed mode of the EBSD detector. Recorded separately from the pattern resolution it implies: the two are distinct settings even though the source states them together as "Speed 1 (622 x 512 pixels)".</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2700,12 +2690,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>Controlled list</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>622 x 512 pixels</t>
+          <t>Speed 1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2725,19 +2715,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>622 x 512 pixels</t>
+          <t>Speed 1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EBSD Camera Gain</t>
+          <t>EBSD Pattern Resolution</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gain applied to the EBSD camera.</t>
+          <t>Pattern resolution in detector pixels, the second half of the source's "Speed 1 (622 x 512 pixels)".</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2752,17 +2742,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>622 x 512 pixels</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Constant in all 14 documents. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Constant in the 12 documents that state it. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2777,19 +2767,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>622 x 512 pixels</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hough Resolution</t>
+          <t>EBSD Camera Gain</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hough transform resolution used for band detection.</t>
+          <t>Gain applied to the EBSD camera.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2799,7 +2789,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Editable</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2809,12 +2799,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60 (observed 45, 60)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Constant in all 14 documents. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2829,19 +2819,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Minimum Bands for Indexing</t>
+          <t>Hough Resolution</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Minimum number of Kikuchi bands required to index a pattern.</t>
+          <t>Hough transform resolution used for band detection.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2851,7 +2841,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Read-Only</t>
+          <t>Editable</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2861,12 +2851,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60 (observed 45, 60)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Stated as "a minimum of five bands"; typically ~10 in practice. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2881,19 +2871,19 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Maximum Mean Angular Deviation</t>
+          <t>Minimum Bands for Indexing</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Upper threshold on mean angular deviation (MAD) for an accepted solution.</t>
+          <t>Minimum number of Kikuchi bands required to index a pattern.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2908,17 +2898,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.2 deg</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Constant in all 14; mean MAD of indexed phases typically below 0.8 deg. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Stated as "a minimum of five bands"; typically ~10 in practice. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2933,29 +2923,29 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1.2 deg</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Map Step Size</t>
+          <t>Maximum Mean Angular Deviation</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Step size of the EBSD map.</t>
+          <t>Upper threshold on mean angular deviation (MAD) for an accepted solution.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2965,12 +2955,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60-600 nm</t>
+          <t>1.2 deg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Mostly given in per-sample tables rather than the prose. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Constant in all 14; mean MAD of indexed phases typically below 0.8 deg. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2985,19 +2975,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>60-600 nm</t>
+          <t>1.2 deg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EBSD Indexing Rate</t>
+          <t>Map Step Size</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pattern collection and indexing rate.</t>
+          <t>Step size of the EBSD map.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3017,12 +3007,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>45-1005 points per second (observed 44 to 1005)</t>
+          <t>60-600 nm</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Mostly given in per-sample tables rather than the prose. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3037,44 +3027,44 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>~45-1005 points per second</t>
+          <t>60-600 nm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EDS Detector</t>
+          <t>EBSD Indexing Rate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EDS detector coupled to the EBSD system.</t>
+          <t>Pattern collection and indexing rate.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Read-Only</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>Number + unit</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>XMax 150 mm SDD</t>
+          <t>45-1005 points per second (observed 44 to 1005)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Constant in all 14 documents. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3089,19 +3079,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>XMax 150 mm SDD</t>
+          <t>~45-1005 points per second</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EDS Channels</t>
+          <t>EDS Detector</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Number of channels EDS spectra are collected on.</t>
+          <t>EDS detector coupled to the EBSD system.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3111,22 +3101,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Editable</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2024 (observed 1024, 2024)</t>
+          <t>XMax 150 mm SDD</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+          <t>Constant in all 14 documents. Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3141,19 +3131,19 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>XMax 150 mm SDD</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EDS Process Time</t>
+          <t>EDS Channels</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AZtec process time setting for EDS.</t>
+          <t>Number of channels EDS spectra are collected on.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3173,7 +3163,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>5 (observed 4, 5)</t>
+          <t>2024 (observed 1024, 2024)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3193,57 +3183,109 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>EDS Process Time</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AZtec process time setting for EDS.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5 (observed 4, 5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Crystal Structure File Sources</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Databases the match units / crystal structure files were drawn from.</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>HKL; ICSD; American Mineralogist</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Seeded 2026-10-07 from the 14 distinct CUWA method-description PDFs; the Example cell gives the observed range.</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>HKL; ICSD; American Mineralogist</t>
         </is>

--- a/draftTAPPs/EBSD_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/EBSD_TAPP_draft_v2.xlsx
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>How this draft was produced.</t>
+          <t>Provenance of this TAPP definition: how the definition itself came to be, as distinct from the method it describes. Use it to state that the definition was transcribed from a published protocol, derived from existing metadata records rather than authored by the laboratory, or produced automatically and reviewed by a person. Optional -- a laboratory-authored TAPP needs nothing here. Recorded on schema:creator.schema:description.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">

--- a/draftTAPPs/EBSD_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/EBSD_TAPP_draft_v2.xlsx
@@ -2430,7 +2430,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (kV)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (nA)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (deg)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (mm)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (ms)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (deg)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (nm)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (points/s)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
